--- a/Praktek Komputer - Spreadsheet/04- Fungsi Matematika/04- Fungsi Matematika.xlsx
+++ b/Praktek Komputer - Spreadsheet/04- Fungsi Matematika/04- Fungsi Matematika.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yamin Folder\Praktek Komputer\Bahan Praktek\48 Rumus Excell\04- Fungsi Matematika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AY Labs\UIN Bukittinggi\Praktek Komputer\Prakom - Belajar Rumus Excell\04- Fungsi Matematika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2055F0E5-BB78-442A-9680-C36844B90367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E07157E-A323-437C-A755-B7A929EBC0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="935" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="935" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RUMUS" sheetId="10" r:id="rId1"/>
@@ -484,12 +484,8 @@
     <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -499,8 +495,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
@@ -817,8 +817,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C49"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" customWidth="1"/>
     <col min="2" max="2" width="20" style="2" customWidth="1"/>
@@ -826,10 +826,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="25" t="s">
         <v>0</v>
       </c>
     </row>
@@ -929,42 +929,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:3" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:3" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B10" location="FLOOR!A1" display="FLOOR" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
@@ -1024,8 +988,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1069,16 +1033,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1124,16 +1088,16 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1187,8 +1151,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1850,8 +1814,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1903,8 +1867,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1956,8 +1920,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2009,8 +1973,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="26.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
